--- a/artfynd/A 65163-2020 artfynd.xlsx
+++ b/artfynd/A 65163-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65163-2020 artfynd.xlsx
+++ b/artfynd/A 65163-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2682,375 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129616686</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57857</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Röhälla, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>592126</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6286298</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129616697</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57320</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Röhälla, Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>592126</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6286298</v>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129616672</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58097</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Röhälla, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>592126</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6286298</v>
+      </c>
+      <c r="S20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65163-2020 artfynd.xlsx
+++ b/artfynd/A 65163-2020 artfynd.xlsx
@@ -2687,7 +2687,7 @@
         <v>129616686</v>
       </c>
       <c r="B18" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>129616697</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>57323</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>129616672</v>
       </c>
       <c r="B20" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 65163-2020 artfynd.xlsx
+++ b/artfynd/A 65163-2020 artfynd.xlsx
@@ -2687,7 +2687,7 @@
         <v>129616686</v>
       </c>
       <c r="B18" t="n">
-        <v>57860</v>
+        <v>57865</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>129616697</v>
       </c>
       <c r="B19" t="n">
-        <v>57323</v>
+        <v>57328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>129616672</v>
       </c>
       <c r="B20" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 65163-2020 artfynd.xlsx
+++ b/artfynd/A 65163-2020 artfynd.xlsx
@@ -2687,7 +2687,7 @@
         <v>129616686</v>
       </c>
       <c r="B18" t="n">
-        <v>57865</v>
+        <v>57866</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>129616697</v>
       </c>
       <c r="B19" t="n">
-        <v>57328</v>
+        <v>57329</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>129616672</v>
       </c>
       <c r="B20" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 65163-2020 artfynd.xlsx
+++ b/artfynd/A 65163-2020 artfynd.xlsx
@@ -2810,7 +2810,7 @@
         <v>129616697</v>
       </c>
       <c r="B19" t="n">
-        <v>57329</v>
+        <v>57330</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>129616672</v>
       </c>
       <c r="B20" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 65163-2020 artfynd.xlsx
+++ b/artfynd/A 65163-2020 artfynd.xlsx
@@ -2687,7 +2687,7 @@
         <v>129616686</v>
       </c>
       <c r="B18" t="n">
-        <v>57866</v>
+        <v>57869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>129616697</v>
       </c>
       <c r="B19" t="n">
-        <v>57330</v>
+        <v>57333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>129616672</v>
       </c>
       <c r="B20" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
